--- a/LRN.WebApp/wwwroot/ImportTemplate/AccessionPaymentReports_Template.xlsx
+++ b/LRN.WebApp/wwwroot/ImportTemplate/AccessionPaymentReports_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Downloads\OneDrive_1_7-30-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D93268-5759-4C0D-95EE-1B454297ECFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E610EA11-195C-447F-A376-768F186D81B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{544E72B6-315A-4B2B-BE7A-9E1CA966ECB8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>RecordId</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Visit#</t>
-  </si>
-  <si>
     <t>AMD Insurance</t>
   </si>
   <si>
@@ -96,6 +93,18 @@
   </si>
   <si>
     <t>BillStatus</t>
+  </si>
+  <si>
+    <t>Billed Application</t>
+  </si>
+  <si>
+    <t>AMD Visit#</t>
+  </si>
+  <si>
+    <t>CMD Visit#</t>
+  </si>
+  <si>
+    <t>FirstBilledDate</t>
   </si>
 </sst>
 </file>
@@ -114,20 +123,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,7 +147,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <fgColor theme="3" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -170,15 +187,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -515,31 +536,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7367A371-915E-4AFD-A893-224EC77195C6}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="44.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="189.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,55 +575,64 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/LRN.WebApp/wwwroot/ImportTemplate/AccessionPaymentReports_Template.xlsx
+++ b/LRN.WebApp/wwwroot/ImportTemplate/AccessionPaymentReports_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Downloads\OneDrive_1_7-30-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E610EA11-195C-447F-A376-768F186D81B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D93268-5759-4C0D-95EE-1B454297ECFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{544E72B6-315A-4B2B-BE7A-9E1CA966ECB8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>RecordId</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Visit#</t>
+  </si>
+  <si>
     <t>AMD Insurance</t>
   </si>
   <si>
@@ -93,18 +96,6 @@
   </si>
   <si>
     <t>BillStatus</t>
-  </si>
-  <si>
-    <t>Billed Application</t>
-  </si>
-  <si>
-    <t>AMD Visit#</t>
-  </si>
-  <si>
-    <t>CMD Visit#</t>
-  </si>
-  <si>
-    <t>FirstBilledDate</t>
   </si>
 </sst>
 </file>
@@ -123,22 +114,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,13 +136,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="-0.249977111117893"/>
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -187,19 +170,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -536,35 +515,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7367A371-915E-4AFD-A893-224EC77195C6}">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="189.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,64 +550,55 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
